--- a/artfynd/A 52014-2024 artfynd.xlsx
+++ b/artfynd/A 52014-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>132760763</v>
       </c>
       <c r="B2" t="n">
-        <v>102938</v>
+        <v>103196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
